--- a/Kamplogg FCSP.xlsx
+++ b/Kamplogg FCSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30408"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Desktop\Privat\Partisan Lillestrøm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="462" documentId="13_ncr:1_{13C26D5C-C8A7-4B63-813B-201D061E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{86F61455-364F-4411-B4B1-66DFB821E4A3}"/>
+  <xr:revisionPtr revIDLastSave="478" documentId="13_ncr:1_{13C26D5C-C8A7-4B63-813B-201D061E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E4D1BE0-CB70-4579-A092-D7F346A03782}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="67">
   <si>
     <t>Kamplogg  - Partisan Lillestrøm</t>
   </si>
@@ -1139,7 +1139,7 @@
   <dimension ref="A1:Y80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
-    <col min="1" max="1" width="4.625" hidden="1" customWidth="1"/>
+    <col min="1" max="1" width="8.5" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.75" bestFit="1" customWidth="1"/>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I2" s="38">
         <f>SUM(I3:I5)</f>
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="J2" s="39">
         <f>I2/$I$2</f>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="J3" s="16">
         <f>I3/$I$2</f>
-        <v>0.48</v>
+        <v>0.47058823529411764</v>
       </c>
       <c r="K3" s="45"/>
     </row>
@@ -1256,11 +1256,11 @@
       </c>
       <c r="I4" s="14">
         <f>SUMIF(F3:F360,"Uavgjort",A3:A360)</f>
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J4" s="18">
         <f t="shared" ref="J3:J5" si="0">I4/$I$2</f>
-        <v>0.24</v>
+        <v>0.25490196078431371</v>
       </c>
       <c r="K4" s="45"/>
     </row>
@@ -1293,7 +1293,7 @@
       </c>
       <c r="J5" s="21">
         <f t="shared" si="0"/>
-        <v>0.28000000000000003</v>
+        <v>0.27450980392156865</v>
       </c>
       <c r="K5" s="45"/>
     </row>
@@ -2473,11 +2473,24 @@
       <c r="K52" s="44"/>
     </row>
     <row r="53" spans="1:11">
-      <c r="B53" s="24"/>
-      <c r="C53" s="1"/>
-      <c r="D53" s="5"/>
-      <c r="E53" s="48"/>
-      <c r="F53" s="10"/>
+      <c r="A53" s="36">
+        <v>1</v>
+      </c>
+      <c r="B53" s="24">
+        <v>46243</v>
+      </c>
+      <c r="C53" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="E53" s="48" t="s">
+        <v>19</v>
+      </c>
+      <c r="F53" s="10" t="s">
+        <v>20</v>
+      </c>
       <c r="G53" s="44"/>
       <c r="H53" s="44"/>
       <c r="I53" s="44"/>
@@ -2485,6 +2498,9 @@
       <c r="K53" s="44"/>
     </row>
     <row r="54" spans="1:11">
+      <c r="A54" s="36">
+        <v>1</v>
+      </c>
       <c r="B54" s="24"/>
       <c r="C54" s="1"/>
       <c r="D54" s="5"/>
@@ -2497,6 +2513,9 @@
       <c r="K54" s="44"/>
     </row>
     <row r="55" spans="1:11" s="44" customFormat="1">
+      <c r="A55" s="36">
+        <v>1</v>
+      </c>
       <c r="B55" s="24"/>
       <c r="C55" s="1"/>
       <c r="D55" s="5"/>
@@ -2504,6 +2523,9 @@
       <c r="F55" s="10"/>
     </row>
     <row r="56" spans="1:11" s="44" customFormat="1">
+      <c r="A56" s="36">
+        <v>1</v>
+      </c>
       <c r="B56" s="24"/>
       <c r="C56" s="1"/>
       <c r="D56" s="5"/>
@@ -2511,6 +2533,9 @@
       <c r="F56" s="10"/>
     </row>
     <row r="57" spans="1:11" s="44" customFormat="1">
+      <c r="A57" s="36">
+        <v>1</v>
+      </c>
       <c r="B57" s="24"/>
       <c r="C57" s="1"/>
       <c r="D57" s="5"/>
@@ -2518,6 +2543,9 @@
       <c r="F57" s="10"/>
     </row>
     <row r="58" spans="1:11" s="44" customFormat="1">
+      <c r="A58" s="36">
+        <v>1</v>
+      </c>
       <c r="B58" s="24"/>
       <c r="C58" s="1"/>
       <c r="D58" s="5"/>
@@ -2525,6 +2553,9 @@
       <c r="F58" s="10"/>
     </row>
     <row r="59" spans="1:11" s="44" customFormat="1">
+      <c r="A59" s="36">
+        <v>1</v>
+      </c>
       <c r="B59" s="24"/>
       <c r="C59" s="1"/>
       <c r="D59" s="5"/>
@@ -2532,32 +2563,125 @@
       <c r="F59" s="10"/>
     </row>
     <row r="60" spans="1:11" s="44" customFormat="1">
+      <c r="A60" s="36">
+        <v>1</v>
+      </c>
       <c r="B60" s="24"/>
       <c r="C60" s="1"/>
       <c r="D60" s="5"/>
       <c r="E60" s="48"/>
       <c r="F60" s="10"/>
     </row>
-    <row r="61" spans="1:11" s="44" customFormat="1"/>
-    <row r="62" spans="1:11" s="44" customFormat="1"/>
-    <row r="63" spans="1:11" s="44" customFormat="1"/>
-    <row r="64" spans="1:11" s="44" customFormat="1"/>
-    <row r="65" s="44" customFormat="1"/>
-    <row r="66" s="44" customFormat="1"/>
-    <row r="67" s="44" customFormat="1"/>
-    <row r="68" s="44" customFormat="1"/>
-    <row r="69" s="44" customFormat="1"/>
-    <row r="70" s="44" customFormat="1"/>
-    <row r="71" s="44" customFormat="1"/>
-    <row r="72" s="44" customFormat="1"/>
-    <row r="73" s="44" customFormat="1"/>
-    <row r="74" s="44" customFormat="1"/>
-    <row r="75" s="44" customFormat="1"/>
-    <row r="76" s="44" customFormat="1"/>
-    <row r="77" s="44" customFormat="1"/>
-    <row r="78" s="44" customFormat="1"/>
-    <row r="79" s="44" customFormat="1"/>
-    <row r="80" s="44" customFormat="1"/>
+    <row r="61" spans="1:11" s="44" customFormat="1">
+      <c r="A61" s="36">
+        <v>1</v>
+      </c>
+      <c r="B61" s="24"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="5"/>
+      <c r="E61" s="48"/>
+      <c r="F61" s="10"/>
+    </row>
+    <row r="62" spans="1:11" s="44" customFormat="1">
+      <c r="A62" s="36">
+        <v>1</v>
+      </c>
+      <c r="B62" s="24"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="5"/>
+      <c r="E62" s="48"/>
+      <c r="F62" s="10"/>
+    </row>
+    <row r="63" spans="1:11" s="44" customFormat="1">
+      <c r="A63" s="36">
+        <v>1</v>
+      </c>
+      <c r="B63" s="24"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="5"/>
+      <c r="E63" s="48"/>
+      <c r="F63" s="10"/>
+    </row>
+    <row r="64" spans="1:11" s="44" customFormat="1">
+      <c r="A64" s="36">
+        <v>1</v>
+      </c>
+      <c r="B64" s="24"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="5"/>
+      <c r="E64" s="48"/>
+      <c r="F64" s="10"/>
+    </row>
+    <row r="65" spans="1:6" s="44" customFormat="1">
+      <c r="A65" s="36">
+        <v>1</v>
+      </c>
+      <c r="B65" s="24"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="5"/>
+      <c r="E65" s="48"/>
+      <c r="F65" s="10"/>
+    </row>
+    <row r="66" spans="1:6" s="44" customFormat="1">
+      <c r="A66" s="36">
+        <v>1</v>
+      </c>
+      <c r="B66" s="24"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="5"/>
+      <c r="E66" s="48"/>
+      <c r="F66" s="10"/>
+    </row>
+    <row r="67" spans="1:6" s="44" customFormat="1">
+      <c r="A67" s="36">
+        <v>1</v>
+      </c>
+      <c r="B67" s="24"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="5"/>
+      <c r="E67" s="48"/>
+      <c r="F67" s="10"/>
+    </row>
+    <row r="68" spans="1:6" s="44" customFormat="1">
+      <c r="A68" s="36">
+        <v>1</v>
+      </c>
+      <c r="B68" s="24"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="5"/>
+      <c r="E68" s="48"/>
+      <c r="F68" s="10"/>
+    </row>
+    <row r="69" spans="1:6" s="44" customFormat="1">
+      <c r="A69" s="36">
+        <v>1</v>
+      </c>
+      <c r="B69" s="24"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="5"/>
+      <c r="E69" s="48"/>
+      <c r="F69" s="10"/>
+    </row>
+    <row r="70" spans="1:6" s="44" customFormat="1">
+      <c r="A70" s="36">
+        <v>1</v>
+      </c>
+      <c r="B70" s="24"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="5"/>
+      <c r="E70" s="48"/>
+      <c r="F70" s="10"/>
+    </row>
+    <row r="71" spans="1:6" s="44" customFormat="1"/>
+    <row r="72" spans="1:6" s="44" customFormat="1"/>
+    <row r="73" spans="1:6" s="44" customFormat="1"/>
+    <row r="74" spans="1:6" s="44" customFormat="1"/>
+    <row r="75" spans="1:6" s="44" customFormat="1"/>
+    <row r="76" spans="1:6" s="44" customFormat="1"/>
+    <row r="77" spans="1:6" s="44" customFormat="1"/>
+    <row r="78" spans="1:6" s="44" customFormat="1"/>
+    <row r="79" spans="1:6" s="44" customFormat="1"/>
+    <row r="80" spans="1:6" s="44" customFormat="1"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B1:E1"/>

--- a/Kamplogg FCSP.xlsx
+++ b/Kamplogg FCSP.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30408"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30431"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bjorn\Desktop\Privat\Partisan Lillestrøm\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="478" documentId="13_ncr:1_{13C26D5C-C8A7-4B63-813B-201D061E3392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3E4D1BE0-CB70-4579-A092-D7F346A03782}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{F5FACD5D-8BEA-4757-BA2F-6C2596D4E4BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="216" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="220" uniqueCount="67">
   <si>
     <t>Kamplogg  - Partisan Lillestrøm</t>
   </si>
@@ -1190,7 +1190,7 @@
       </c>
       <c r="I2" s="38">
         <f>SUM(I3:I5)</f>
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="J2" s="39">
         <f>I2/$I$2</f>
@@ -1227,7 +1227,7 @@
       </c>
       <c r="J3" s="16">
         <f>I3/$I$2</f>
-        <v>0.47058823529411764</v>
+        <v>0.46153846153846156</v>
       </c>
       <c r="K3" s="45"/>
     </row>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="J4" s="18">
         <f t="shared" ref="J3:J5" si="0">I4/$I$2</f>
-        <v>0.25490196078431371</v>
+        <v>0.25</v>
       </c>
       <c r="K4" s="45"/>
     </row>
@@ -1289,11 +1289,11 @@
       </c>
       <c r="I5" s="20">
         <f>SUMIF(F3:F360,"Tap",A3:A360)</f>
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J5" s="21">
         <f t="shared" si="0"/>
-        <v>0.27450980392156865</v>
+        <v>0.28846153846153844</v>
       </c>
       <c r="K5" s="45"/>
     </row>
@@ -2501,11 +2501,21 @@
       <c r="A54" s="36">
         <v>1</v>
       </c>
-      <c r="B54" s="24"/>
-      <c r="C54" s="1"/>
-      <c r="D54" s="5"/>
-      <c r="E54" s="48"/>
-      <c r="F54" s="10"/>
+      <c r="B54" s="24">
+        <v>46264</v>
+      </c>
+      <c r="C54" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="E54" s="48" t="s">
+        <v>32</v>
+      </c>
+      <c r="F54" s="10" t="s">
+        <v>17</v>
+      </c>
       <c r="G54" s="44"/>
       <c r="H54" s="44"/>
       <c r="I54" s="44"/>
